--- a/auto_repair/public/www/assets/xlsx/si-6.xlsx
+++ b/auto_repair/public/www/assets/xlsx/si-6.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\auto-repair-erp\web\src\assets\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488DB312-06B9-4EF6-B626-AA192E0231A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="Accounts" sheetId="1" r:id="rId1"/>
-    <sheet name="Departments" sheetId="2" r:id="rId2"/>
-    <sheet name="Employees" sheetId="3" r:id="rId3"/>
-    <sheet name="Categories" sheetId="4" r:id="rId4"/>
-    <sheet name="Segments" sheetId="5" r:id="rId5"/>
-    <sheet name="Services" sheetId="6" r:id="rId6"/>
-    <sheet name="Stock" sheetId="7" r:id="rId7"/>
-    <sheet name="Work Stations" sheetId="8" r:id="rId8"/>
-    <sheet name="Presets" sheetId="9" r:id="rId9"/>
+    <sheet name="Accounts" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Departments" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Employees" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Categories" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Segments" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Services" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Stock" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Presets" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -33,316 +27,318 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="98">
-  <si>
-    <t>account_name</t>
-  </si>
-  <si>
-    <t>parent_account</t>
-  </si>
-  <si>
-    <t>account_type</t>
-  </si>
-  <si>
-    <t>account_number</t>
-  </si>
-  <si>
-    <t>Bank</t>
-  </si>
-  <si>
-    <t>department_name</t>
-  </si>
-  <si>
-    <t>employee_name</t>
-  </si>
-  <si>
-    <t>gender</t>
-  </si>
-  <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
-    <t>date_of_joining</t>
-  </si>
-  <si>
-    <t>cell_number</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>salary_mode</t>
-  </si>
-  <si>
-    <t>ctc</t>
-  </si>
-  <si>
-    <t>bank_name</t>
-  </si>
-  <si>
-    <t>bank_ac_no</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>ceo</t>
-  </si>
-  <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>accounting-manager</t>
-  </si>
-  <si>
-    <t>hr-manager</t>
-  </si>
-  <si>
-    <t>manufacturing-manager</t>
-  </si>
-  <si>
-    <t>Cheque</t>
-  </si>
-  <si>
-    <t>garage-foreman</t>
-  </si>
-  <si>
-    <t>garage-technician</t>
-  </si>
-  <si>
-    <t>pos-manager</t>
-  </si>
-  <si>
-    <t>pos-clerk</t>
-  </si>
-  <si>
-    <t>super-user</t>
-  </si>
-  <si>
-    <t>item_group_name</t>
-  </si>
-  <si>
-    <t>parent_item_group</t>
-  </si>
-  <si>
-    <t>item_code</t>
-  </si>
-  <si>
-    <t>item_group</t>
-  </si>
-  <si>
-    <t>item_name</t>
-  </si>
-  <si>
-    <t>standard_rate</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>opening_stock</t>
-  </si>
-  <si>
-    <t>valuation_rate</t>
-  </si>
-  <si>
-    <t>is_stock_item</t>
-  </si>
-  <si>
-    <t>stock_uom</t>
-  </si>
-  <si>
-    <t>Nos</t>
-  </si>
-  <si>
-    <t>workstation_name</t>
-  </si>
-  <si>
-    <t>hour_rate_electricity</t>
-  </si>
-  <si>
-    <t>hour_rate_consumable</t>
-  </si>
-  <si>
-    <t>hour_rate_rent</t>
-  </si>
-  <si>
-    <t>hour_rate_labour</t>
-  </si>
-  <si>
-    <t>Types</t>
-  </si>
-  <si>
-    <t>Genders</t>
-  </si>
-  <si>
-    <t>Salary Mode</t>
-  </si>
-  <si>
-    <t>uom</t>
-  </si>
-  <si>
-    <t>roles</t>
-  </si>
-  <si>
-    <t>Accumulated Depreciation</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Asset Received But Not Billed</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Box</t>
-  </si>
-  <si>
-    <t>financial-manager</t>
-  </si>
-  <si>
-    <t>financial-clerk</t>
-  </si>
-  <si>
-    <t>Meter</t>
-  </si>
-  <si>
-    <t>Chargeable</t>
-  </si>
-  <si>
-    <t>Centimeter</t>
-  </si>
-  <si>
-    <t>hr-clerk</t>
-  </si>
-  <si>
-    <t>Capital Work in Progress</t>
-  </si>
-  <si>
-    <t>Inch</t>
-  </si>
-  <si>
-    <t>Cost of Goods Sold</t>
-  </si>
-  <si>
-    <t>Rod</t>
-  </si>
-  <si>
-    <t>manufacturing-foreman</t>
-  </si>
-  <si>
-    <t>Depreciation</t>
-  </si>
-  <si>
-    <t>Gram</t>
-  </si>
-  <si>
-    <t>manufacturing-technician</t>
-  </si>
-  <si>
-    <t>Equity</t>
-  </si>
-  <si>
-    <t>Litre</t>
-  </si>
-  <si>
-    <t>project-manager</t>
-  </si>
-  <si>
-    <t>Expense Account</t>
-  </si>
-  <si>
-    <t>Gallon (UK)</t>
-  </si>
-  <si>
-    <t>project-assignee</t>
-  </si>
-  <si>
-    <t>Expenses Included In Asset Valuation</t>
-  </si>
-  <si>
-    <t>Expenses Included In Valuation</t>
-  </si>
-  <si>
-    <t>Fixed Asset</t>
-  </si>
-  <si>
-    <t>Income Account</t>
-  </si>
-  <si>
-    <t>Payable</t>
-  </si>
-  <si>
-    <t>Receivable</t>
-  </si>
-  <si>
-    <t>accounting-clerk</t>
-  </si>
-  <si>
-    <t>Round Off</t>
-  </si>
-  <si>
-    <t>inventory-manager</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>inventory-clerk</t>
-  </si>
-  <si>
-    <t>Stock Adjustment</t>
-  </si>
-  <si>
-    <t>sales-manager</t>
-  </si>
-  <si>
-    <t>Stock Received But Not Billed</t>
-  </si>
-  <si>
-    <t>sales-clerk</t>
-  </si>
-  <si>
-    <t>Service Received But Not Billed</t>
-  </si>
-  <si>
-    <t>procurement-manager</t>
-  </si>
-  <si>
-    <t>Tax</t>
-  </si>
-  <si>
-    <t>procurement-clerk</t>
-  </si>
-  <si>
-    <t>Temporary</t>
-  </si>
-  <si>
-    <t>administrator</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="93">
+  <si>
+    <t xml:space="preserve">account_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parent_account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">account_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">account_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">department_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employee_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_of_birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_of_joining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salary_mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ctc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bank_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bank_ac_no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item_group_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parent_item_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">item_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opening_stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valuation_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_stock_item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stock_uom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accumulated Depreciation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ceo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset Received But Not Billed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">financial-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">financial-clerk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hr-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chargeable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centimeter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hr-clerk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital Work in Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manufacturing-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost of Goods Sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manufacturing-foreman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manufacturing-technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">project-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expense Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gallon (UK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">project-assignee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expenses Included In Asset Valuation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">garage-foreman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expenses Included In Valuation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">garage-technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pos-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pos-clerk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receivable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accounting-clerk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round Off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inventory-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inventory-clerk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock Adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sales-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock Received But Not Billed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sales-clerk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Received But Not Billed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">procurement-manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">procurement-clerk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temporary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">super-user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">administrator</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-809]dd\ mmmm\ yyyy;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="[$-809]dd\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -354,7 +350,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -362,124 +358,165 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+  <cellXfs count="8">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:A24" totalsRowShown="0">
-  <autoFilter ref="A1:A24" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:A24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:A24"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Types"/>
+    <tableColumn id="1" name="Types"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table13" displayName="Table13" ref="C1:C3" totalsRowShown="0">
-  <autoFilter ref="C1:C3" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table13" displayName="Table13" ref="C1:C3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="C1:C3"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Genders"/>
+    <tableColumn id="1" name="Genders"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table2" displayName="Table2" ref="E1:E4" totalsRowShown="0">
-  <autoFilter ref="E1:E4" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table2" displayName="Table2" ref="E1:E4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="E1:E4"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Salary Mode"/>
+    <tableColumn id="1" name="Salary Mode"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table4" displayName="Table4" ref="I1:I25" totalsRowShown="0">
-  <autoFilter ref="I1:I25" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="I1:I25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="I1:I25"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="roles"/>
+    <tableColumn id="1" name="roles"/>
   </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -487,12 +524,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -519,7 +556,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -540,7 +577,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -591,7 +628,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -607,28 +644,29 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -642,90 +680,106 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L1012"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L1001"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="41.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="37.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="37.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -737,7 +791,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="5"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
@@ -750,7 +804,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
@@ -763,7 +817,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
@@ -776,7 +830,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3"/>
@@ -789,7 +843,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3"/>
@@ -802,7 +856,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3"/>
@@ -815,7 +869,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
@@ -828,7 +882,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
@@ -841,7 +895,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3"/>
@@ -854,7 +908,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="3"/>
@@ -867,7 +921,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -879,3162 +933,3152 @@
       <c r="K13" s="2"/>
       <c r="L13" s="5"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G28" s="4"/>
     </row>
-    <row r="29" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G29" s="4"/>
     </row>
-    <row r="30" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G30" s="4"/>
     </row>
-    <row r="31" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G31" s="4"/>
     </row>
-    <row r="32" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G32" s="4"/>
     </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G33" s="4"/>
     </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G34" s="4"/>
     </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G35" s="4"/>
     </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G40" s="4"/>
     </row>
-    <row r="41" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G41" s="4"/>
     </row>
-    <row r="42" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G42" s="4"/>
     </row>
-    <row r="43" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G43" s="4"/>
     </row>
-    <row r="44" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G44" s="4"/>
     </row>
-    <row r="45" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G45" s="4"/>
     </row>
-    <row r="46" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G46" s="4"/>
     </row>
-    <row r="47" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G47" s="4"/>
     </row>
-    <row r="48" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G48" s="4"/>
     </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G49" s="4"/>
     </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G50" s="4"/>
     </row>
-    <row r="51" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G51" s="4"/>
     </row>
-    <row r="52" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G52" s="4"/>
     </row>
-    <row r="53" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G53" s="4"/>
     </row>
-    <row r="54" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G54" s="4"/>
     </row>
-    <row r="55" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G55" s="4"/>
     </row>
-    <row r="56" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G56" s="4"/>
     </row>
-    <row r="57" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G57" s="4"/>
     </row>
-    <row r="58" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G58" s="4"/>
     </row>
-    <row r="59" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G59" s="4"/>
     </row>
-    <row r="60" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G60" s="4"/>
     </row>
-    <row r="61" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G61" s="4"/>
     </row>
-    <row r="62" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G62" s="4"/>
     </row>
-    <row r="63" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G63" s="4"/>
     </row>
-    <row r="64" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G64" s="4"/>
     </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G65" s="4"/>
     </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G66" s="4"/>
     </row>
-    <row r="67" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G67" s="4"/>
     </row>
-    <row r="68" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G68" s="4"/>
     </row>
-    <row r="69" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G69" s="4"/>
     </row>
-    <row r="70" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G70" s="4"/>
     </row>
-    <row r="71" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G71" s="4"/>
     </row>
-    <row r="72" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G72" s="4"/>
     </row>
-    <row r="73" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G73" s="4"/>
     </row>
-    <row r="74" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G74" s="4"/>
     </row>
-    <row r="75" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G75" s="4"/>
     </row>
-    <row r="76" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G76" s="4"/>
     </row>
-    <row r="77" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G77" s="4"/>
     </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G78" s="4"/>
     </row>
-    <row r="79" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G79" s="4"/>
     </row>
-    <row r="80" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G80" s="4"/>
     </row>
-    <row r="81" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G81" s="4"/>
     </row>
-    <row r="82" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G82" s="4"/>
     </row>
-    <row r="83" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G83" s="4"/>
     </row>
-    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G84" s="4"/>
     </row>
-    <row r="85" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G85" s="4"/>
     </row>
-    <row r="86" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G86" s="4"/>
     </row>
-    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G87" s="4"/>
     </row>
-    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G88" s="4"/>
     </row>
-    <row r="89" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G89" s="4"/>
     </row>
-    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G90" s="4"/>
     </row>
-    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G91" s="4"/>
     </row>
-    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G92" s="4"/>
     </row>
-    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G93" s="4"/>
     </row>
-    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G94" s="4"/>
     </row>
-    <row r="95" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G95" s="4"/>
     </row>
-    <row r="96" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G96" s="4"/>
     </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G97" s="4"/>
     </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G98" s="4"/>
     </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G99" s="4"/>
     </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G100" s="4"/>
     </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G101" s="4"/>
     </row>
-    <row r="102" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G102" s="4"/>
     </row>
-    <row r="103" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G103" s="4"/>
     </row>
-    <row r="104" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G104" s="4"/>
     </row>
-    <row r="105" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G105" s="4"/>
     </row>
-    <row r="106" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G106" s="4"/>
     </row>
-    <row r="107" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G107" s="4"/>
     </row>
-    <row r="108" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G108" s="4"/>
     </row>
-    <row r="109" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G109" s="4"/>
     </row>
-    <row r="110" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G110" s="4"/>
     </row>
-    <row r="111" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G111" s="4"/>
     </row>
-    <row r="112" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G112" s="4"/>
     </row>
-    <row r="113" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G113" s="4"/>
     </row>
-    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G114" s="4"/>
     </row>
-    <row r="115" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G115" s="4"/>
     </row>
-    <row r="116" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G116" s="4"/>
     </row>
-    <row r="117" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G117" s="4"/>
     </row>
-    <row r="118" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G118" s="4"/>
     </row>
-    <row r="119" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G119" s="4"/>
     </row>
-    <row r="120" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G120" s="4"/>
     </row>
-    <row r="121" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G121" s="4"/>
     </row>
-    <row r="122" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G122" s="4"/>
     </row>
-    <row r="123" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G123" s="4"/>
     </row>
-    <row r="124" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G124" s="4"/>
     </row>
-    <row r="125" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G125" s="4"/>
     </row>
-    <row r="126" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G126" s="4"/>
     </row>
-    <row r="127" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G127" s="4"/>
     </row>
-    <row r="128" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G128" s="4"/>
     </row>
-    <row r="129" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G129" s="4"/>
     </row>
-    <row r="130" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G130" s="4"/>
     </row>
-    <row r="131" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G131" s="4"/>
     </row>
-    <row r="132" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G132" s="4"/>
     </row>
-    <row r="133" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G133" s="4"/>
     </row>
-    <row r="134" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G134" s="4"/>
     </row>
-    <row r="135" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G135" s="4"/>
     </row>
-    <row r="136" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G136" s="4"/>
     </row>
-    <row r="137" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G137" s="4"/>
     </row>
-    <row r="138" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G138" s="4"/>
     </row>
-    <row r="139" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G139" s="4"/>
     </row>
-    <row r="140" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G140" s="4"/>
     </row>
-    <row r="141" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G141" s="4"/>
     </row>
-    <row r="142" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G142" s="4"/>
     </row>
-    <row r="143" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G143" s="4"/>
     </row>
-    <row r="144" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G144" s="4"/>
     </row>
-    <row r="145" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G145" s="4"/>
     </row>
-    <row r="146" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G146" s="4"/>
     </row>
-    <row r="147" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G147" s="4"/>
     </row>
-    <row r="148" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G148" s="4"/>
     </row>
-    <row r="149" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G149" s="4"/>
     </row>
-    <row r="150" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G150" s="4"/>
     </row>
-    <row r="151" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G151" s="4"/>
     </row>
-    <row r="152" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G152" s="4"/>
     </row>
-    <row r="153" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G153" s="4"/>
     </row>
-    <row r="154" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G154" s="4"/>
     </row>
-    <row r="155" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G155" s="4"/>
     </row>
-    <row r="156" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G156" s="4"/>
     </row>
-    <row r="157" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G157" s="4"/>
     </row>
-    <row r="158" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G158" s="4"/>
     </row>
-    <row r="159" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G159" s="4"/>
     </row>
-    <row r="160" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G160" s="4"/>
     </row>
-    <row r="161" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G161" s="4"/>
     </row>
-    <row r="162" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G162" s="4"/>
     </row>
-    <row r="163" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G163" s="4"/>
     </row>
-    <row r="164" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G164" s="4"/>
     </row>
-    <row r="165" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G165" s="4"/>
     </row>
-    <row r="166" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G166" s="4"/>
     </row>
-    <row r="167" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G167" s="4"/>
     </row>
-    <row r="168" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G168" s="4"/>
     </row>
-    <row r="169" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G169" s="4"/>
     </row>
-    <row r="170" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G170" s="4"/>
     </row>
-    <row r="171" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G171" s="4"/>
     </row>
-    <row r="172" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G172" s="4"/>
     </row>
-    <row r="173" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G173" s="4"/>
     </row>
-    <row r="174" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G174" s="4"/>
     </row>
-    <row r="175" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G175" s="4"/>
     </row>
-    <row r="176" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G176" s="4"/>
     </row>
-    <row r="177" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G177" s="4"/>
     </row>
-    <row r="178" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G178" s="4"/>
     </row>
-    <row r="179" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G179" s="4"/>
     </row>
-    <row r="180" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G180" s="4"/>
     </row>
-    <row r="181" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G181" s="4"/>
     </row>
-    <row r="182" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G182" s="4"/>
     </row>
-    <row r="183" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G183" s="4"/>
     </row>
-    <row r="184" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G184" s="4"/>
     </row>
-    <row r="185" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G185" s="4"/>
     </row>
-    <row r="186" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G186" s="4"/>
     </row>
-    <row r="187" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G187" s="4"/>
     </row>
-    <row r="188" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G188" s="4"/>
     </row>
-    <row r="189" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G189" s="4"/>
     </row>
-    <row r="190" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G190" s="4"/>
     </row>
-    <row r="191" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G191" s="4"/>
     </row>
-    <row r="192" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G192" s="4"/>
     </row>
-    <row r="193" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G193" s="4"/>
     </row>
-    <row r="194" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G194" s="4"/>
     </row>
-    <row r="195" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G195" s="4"/>
     </row>
-    <row r="196" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G196" s="4"/>
     </row>
-    <row r="197" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G197" s="4"/>
     </row>
-    <row r="198" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G198" s="4"/>
     </row>
-    <row r="199" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G199" s="4"/>
     </row>
-    <row r="200" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G200" s="4"/>
     </row>
-    <row r="201" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G201" s="4"/>
     </row>
-    <row r="202" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G202" s="4"/>
     </row>
-    <row r="203" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G203" s="4"/>
     </row>
-    <row r="204" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G204" s="4"/>
     </row>
-    <row r="205" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G205" s="4"/>
     </row>
-    <row r="206" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G206" s="4"/>
     </row>
-    <row r="207" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G207" s="4"/>
     </row>
-    <row r="208" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G208" s="4"/>
     </row>
-    <row r="209" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G209" s="4"/>
     </row>
-    <row r="210" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G210" s="4"/>
     </row>
-    <row r="211" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G211" s="4"/>
     </row>
-    <row r="212" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G212" s="4"/>
     </row>
-    <row r="213" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G213" s="4"/>
     </row>
-    <row r="214" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G214" s="4"/>
     </row>
-    <row r="215" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G215" s="4"/>
     </row>
-    <row r="216" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G216" s="4"/>
     </row>
-    <row r="217" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G217" s="4"/>
     </row>
-    <row r="218" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G218" s="4"/>
     </row>
-    <row r="219" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G219" s="4"/>
     </row>
-    <row r="220" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G220" s="4"/>
     </row>
-    <row r="221" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G221" s="4"/>
     </row>
-    <row r="222" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G222" s="4"/>
     </row>
-    <row r="223" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G223" s="4"/>
     </row>
-    <row r="224" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G224" s="4"/>
     </row>
-    <row r="225" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G225" s="4"/>
     </row>
-    <row r="226" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G226" s="4"/>
     </row>
-    <row r="227" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G227" s="4"/>
     </row>
-    <row r="228" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G228" s="4"/>
     </row>
-    <row r="229" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G229" s="4"/>
     </row>
-    <row r="230" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G230" s="4"/>
     </row>
-    <row r="231" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G231" s="4"/>
     </row>
-    <row r="232" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G232" s="4"/>
     </row>
-    <row r="233" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G233" s="4"/>
     </row>
-    <row r="234" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G234" s="4"/>
     </row>
-    <row r="235" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G235" s="4"/>
     </row>
-    <row r="236" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G236" s="4"/>
     </row>
-    <row r="237" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G237" s="4"/>
     </row>
-    <row r="238" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G238" s="4"/>
     </row>
-    <row r="239" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G239" s="4"/>
     </row>
-    <row r="240" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G240" s="4"/>
     </row>
-    <row r="241" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G241" s="4"/>
     </row>
-    <row r="242" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G242" s="4"/>
     </row>
-    <row r="243" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G243" s="4"/>
     </row>
-    <row r="244" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G244" s="4"/>
     </row>
-    <row r="245" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G245" s="4"/>
     </row>
-    <row r="246" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G246" s="4"/>
     </row>
-    <row r="247" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G247" s="4"/>
     </row>
-    <row r="248" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G248" s="4"/>
     </row>
-    <row r="249" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G249" s="4"/>
     </row>
-    <row r="250" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G250" s="4"/>
     </row>
-    <row r="251" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G251" s="4"/>
     </row>
-    <row r="252" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G252" s="4"/>
     </row>
-    <row r="253" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G253" s="4"/>
     </row>
-    <row r="254" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G254" s="4"/>
     </row>
-    <row r="255" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G255" s="4"/>
     </row>
-    <row r="256" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G256" s="4"/>
     </row>
-    <row r="257" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G257" s="4"/>
     </row>
-    <row r="258" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G258" s="4"/>
     </row>
-    <row r="259" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G259" s="4"/>
     </row>
-    <row r="260" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G260" s="4"/>
     </row>
-    <row r="261" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G261" s="4"/>
     </row>
-    <row r="262" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G262" s="4"/>
     </row>
-    <row r="263" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G263" s="4"/>
     </row>
-    <row r="264" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G264" s="4"/>
     </row>
-    <row r="265" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G265" s="4"/>
     </row>
-    <row r="266" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G266" s="4"/>
     </row>
-    <row r="267" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G267" s="4"/>
     </row>
-    <row r="268" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G268" s="4"/>
     </row>
-    <row r="269" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G269" s="4"/>
     </row>
-    <row r="270" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G270" s="4"/>
     </row>
-    <row r="271" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G271" s="4"/>
     </row>
-    <row r="272" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G272" s="4"/>
     </row>
-    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G273" s="4"/>
     </row>
-    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G274" s="4"/>
     </row>
-    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G275" s="4"/>
     </row>
-    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G276" s="4"/>
     </row>
-    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G277" s="4"/>
     </row>
-    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G278" s="4"/>
     </row>
-    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G279" s="4"/>
     </row>
-    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G280" s="4"/>
     </row>
-    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G281" s="4"/>
     </row>
-    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G282" s="4"/>
     </row>
-    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G283" s="4"/>
     </row>
-    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G284" s="4"/>
     </row>
-    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G285" s="4"/>
     </row>
-    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G286" s="4"/>
     </row>
-    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G287" s="4"/>
     </row>
-    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G288" s="4"/>
     </row>
-    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G289" s="4"/>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G290" s="4"/>
     </row>
-    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G291" s="4"/>
     </row>
-    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G292" s="4"/>
     </row>
-    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G293" s="4"/>
     </row>
-    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G294" s="4"/>
     </row>
-    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G295" s="4"/>
     </row>
-    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G296" s="4"/>
     </row>
-    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G297" s="4"/>
     </row>
-    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G298" s="4"/>
     </row>
-    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G299" s="4"/>
     </row>
-    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G300" s="4"/>
     </row>
-    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G301" s="4"/>
     </row>
-    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G302" s="4"/>
     </row>
-    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G303" s="4"/>
     </row>
-    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G304" s="4"/>
     </row>
-    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G305" s="4"/>
     </row>
-    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G306" s="4"/>
     </row>
-    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G307" s="4"/>
     </row>
-    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G308" s="4"/>
     </row>
-    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G309" s="4"/>
     </row>
-    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G310" s="4"/>
     </row>
-    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G311" s="4"/>
     </row>
-    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G312" s="4"/>
     </row>
-    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G313" s="4"/>
     </row>
-    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G314" s="4"/>
     </row>
-    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G315" s="4"/>
     </row>
-    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G316" s="4"/>
     </row>
-    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G317" s="4"/>
     </row>
-    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G318" s="4"/>
     </row>
-    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G319" s="4"/>
     </row>
-    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G320" s="4"/>
     </row>
-    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G321" s="4"/>
     </row>
-    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G322" s="4"/>
     </row>
-    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G323" s="4"/>
     </row>
-    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G324" s="4"/>
     </row>
-    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G325" s="4"/>
     </row>
-    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G326" s="4"/>
     </row>
-    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G327" s="4"/>
     </row>
-    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G328" s="4"/>
     </row>
-    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G329" s="4"/>
     </row>
-    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G330" s="4"/>
     </row>
-    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G331" s="4"/>
     </row>
-    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G332" s="4"/>
     </row>
-    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G333" s="4"/>
     </row>
-    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G334" s="4"/>
     </row>
-    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G335" s="4"/>
     </row>
-    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G336" s="4"/>
     </row>
-    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G337" s="4"/>
     </row>
-    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G338" s="4"/>
     </row>
-    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G339" s="4"/>
     </row>
-    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G340" s="4"/>
     </row>
-    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G341" s="4"/>
     </row>
-    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G342" s="4"/>
     </row>
-    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G343" s="4"/>
     </row>
-    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G344" s="4"/>
     </row>
-    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G345" s="4"/>
     </row>
-    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G346" s="4"/>
     </row>
-    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G347" s="4"/>
     </row>
-    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G348" s="4"/>
     </row>
-    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G349" s="4"/>
     </row>
-    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G350" s="4"/>
     </row>
-    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G351" s="4"/>
     </row>
-    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G352" s="4"/>
     </row>
-    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G353" s="4"/>
     </row>
-    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G354" s="4"/>
     </row>
-    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G355" s="4"/>
     </row>
-    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G356" s="4"/>
     </row>
-    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G357" s="4"/>
     </row>
-    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G358" s="4"/>
     </row>
-    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G359" s="4"/>
     </row>
-    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G360" s="4"/>
     </row>
-    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G361" s="4"/>
     </row>
-    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G362" s="4"/>
     </row>
-    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G363" s="4"/>
     </row>
-    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G364" s="4"/>
     </row>
-    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G365" s="4"/>
     </row>
-    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G366" s="4"/>
     </row>
-    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G367" s="4"/>
     </row>
-    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G368" s="4"/>
     </row>
-    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G369" s="4"/>
     </row>
-    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G370" s="4"/>
     </row>
-    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G371" s="4"/>
     </row>
-    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G372" s="4"/>
     </row>
-    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G373" s="4"/>
     </row>
-    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G374" s="4"/>
     </row>
-    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G375" s="4"/>
     </row>
-    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G376" s="4"/>
     </row>
-    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G377" s="4"/>
     </row>
-    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G378" s="4"/>
     </row>
-    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G379" s="4"/>
     </row>
-    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G380" s="4"/>
     </row>
-    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G381" s="4"/>
     </row>
-    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G382" s="4"/>
     </row>
-    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G383" s="4"/>
     </row>
-    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G384" s="4"/>
     </row>
-    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G385" s="4"/>
     </row>
-    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G386" s="4"/>
     </row>
-    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G387" s="4"/>
     </row>
-    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G388" s="4"/>
     </row>
-    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G389" s="4"/>
     </row>
-    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G390" s="4"/>
     </row>
-    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G391" s="4"/>
     </row>
-    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G392" s="4"/>
     </row>
-    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G393" s="4"/>
     </row>
-    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G394" s="4"/>
     </row>
-    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G395" s="4"/>
     </row>
-    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G396" s="4"/>
     </row>
-    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G397" s="4"/>
     </row>
-    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G398" s="4"/>
     </row>
-    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G399" s="4"/>
     </row>
-    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G400" s="4"/>
     </row>
-    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G401" s="4"/>
     </row>
-    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G402" s="4"/>
     </row>
-    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G403" s="4"/>
     </row>
-    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G404" s="4"/>
     </row>
-    <row r="405" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G405" s="4"/>
     </row>
-    <row r="406" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G406" s="4"/>
     </row>
-    <row r="407" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G407" s="4"/>
     </row>
-    <row r="408" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G408" s="4"/>
     </row>
-    <row r="409" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G409" s="4"/>
     </row>
-    <row r="410" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G410" s="4"/>
     </row>
-    <row r="411" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G411" s="4"/>
     </row>
-    <row r="412" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G412" s="4"/>
     </row>
-    <row r="413" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G413" s="4"/>
     </row>
-    <row r="414" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G414" s="4"/>
     </row>
-    <row r="415" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G415" s="4"/>
     </row>
-    <row r="416" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G416" s="4"/>
     </row>
-    <row r="417" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G417" s="4"/>
     </row>
-    <row r="418" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G418" s="4"/>
     </row>
-    <row r="419" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G419" s="4"/>
     </row>
-    <row r="420" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G420" s="4"/>
     </row>
-    <row r="421" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G421" s="4"/>
     </row>
-    <row r="422" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G422" s="4"/>
     </row>
-    <row r="423" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G423" s="4"/>
     </row>
-    <row r="424" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G424" s="4"/>
     </row>
-    <row r="425" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G425" s="4"/>
     </row>
-    <row r="426" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G426" s="4"/>
     </row>
-    <row r="427" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G427" s="4"/>
     </row>
-    <row r="428" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G428" s="4"/>
     </row>
-    <row r="429" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G429" s="4"/>
     </row>
-    <row r="430" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G430" s="4"/>
     </row>
-    <row r="431" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G431" s="4"/>
     </row>
-    <row r="432" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G432" s="4"/>
     </row>
-    <row r="433" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G433" s="4"/>
     </row>
-    <row r="434" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G434" s="4"/>
     </row>
-    <row r="435" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G435" s="4"/>
     </row>
-    <row r="436" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G436" s="4"/>
     </row>
-    <row r="437" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G437" s="4"/>
     </row>
-    <row r="438" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G438" s="4"/>
     </row>
-    <row r="439" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G439" s="4"/>
     </row>
-    <row r="440" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G440" s="4"/>
     </row>
-    <row r="441" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G441" s="4"/>
     </row>
-    <row r="442" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G442" s="4"/>
     </row>
-    <row r="443" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G443" s="4"/>
     </row>
-    <row r="444" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G444" s="4"/>
     </row>
-    <row r="445" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G445" s="4"/>
     </row>
-    <row r="446" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G446" s="4"/>
     </row>
-    <row r="447" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G447" s="4"/>
     </row>
-    <row r="448" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G448" s="4"/>
     </row>
-    <row r="449" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G449" s="4"/>
     </row>
-    <row r="450" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G450" s="4"/>
     </row>
-    <row r="451" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G451" s="4"/>
     </row>
-    <row r="452" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G452" s="4"/>
     </row>
-    <row r="453" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G453" s="4"/>
     </row>
-    <row r="454" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G454" s="4"/>
     </row>
-    <row r="455" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G455" s="4"/>
     </row>
-    <row r="456" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G456" s="4"/>
     </row>
-    <row r="457" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G457" s="4"/>
     </row>
-    <row r="458" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G458" s="4"/>
     </row>
-    <row r="459" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G459" s="4"/>
     </row>
-    <row r="460" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G460" s="4"/>
     </row>
-    <row r="461" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G461" s="4"/>
     </row>
-    <row r="462" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G462" s="4"/>
     </row>
-    <row r="463" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G463" s="4"/>
     </row>
-    <row r="464" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G464" s="4"/>
     </row>
-    <row r="465" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G465" s="4"/>
     </row>
-    <row r="466" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G466" s="4"/>
     </row>
-    <row r="467" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G467" s="4"/>
     </row>
-    <row r="468" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G468" s="4"/>
     </row>
-    <row r="469" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G469" s="4"/>
     </row>
-    <row r="470" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G470" s="4"/>
     </row>
-    <row r="471" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G471" s="4"/>
     </row>
-    <row r="472" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G472" s="4"/>
     </row>
-    <row r="473" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G473" s="4"/>
     </row>
-    <row r="474" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G474" s="4"/>
     </row>
-    <row r="475" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G475" s="4"/>
     </row>
-    <row r="476" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G476" s="4"/>
     </row>
-    <row r="477" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G477" s="4"/>
     </row>
-    <row r="478" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G478" s="4"/>
     </row>
-    <row r="479" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G479" s="4"/>
     </row>
-    <row r="480" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G480" s="4"/>
     </row>
-    <row r="481" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G481" s="4"/>
     </row>
-    <row r="482" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G482" s="4"/>
     </row>
-    <row r="483" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G483" s="4"/>
     </row>
-    <row r="484" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G484" s="4"/>
     </row>
-    <row r="485" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G485" s="4"/>
     </row>
-    <row r="486" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G486" s="4"/>
     </row>
-    <row r="487" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G487" s="4"/>
     </row>
-    <row r="488" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G488" s="4"/>
     </row>
-    <row r="489" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G489" s="4"/>
     </row>
-    <row r="490" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G490" s="4"/>
     </row>
-    <row r="491" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G491" s="4"/>
     </row>
-    <row r="492" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G492" s="4"/>
     </row>
-    <row r="493" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G493" s="4"/>
     </row>
-    <row r="494" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G494" s="4"/>
     </row>
-    <row r="495" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G495" s="4"/>
     </row>
-    <row r="496" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G496" s="4"/>
     </row>
-    <row r="497" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G497" s="4"/>
     </row>
-    <row r="498" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G498" s="4"/>
     </row>
-    <row r="499" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G499" s="4"/>
     </row>
-    <row r="500" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G500" s="4"/>
     </row>
-    <row r="501" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G501" s="4"/>
     </row>
-    <row r="502" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G502" s="4"/>
     </row>
-    <row r="503" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G503" s="4"/>
     </row>
-    <row r="504" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G504" s="4"/>
     </row>
-    <row r="505" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G505" s="4"/>
     </row>
-    <row r="506" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G506" s="4"/>
     </row>
-    <row r="507" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G507" s="4"/>
     </row>
-    <row r="508" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G508" s="4"/>
     </row>
-    <row r="509" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G509" s="4"/>
     </row>
-    <row r="510" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G510" s="4"/>
     </row>
-    <row r="511" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G511" s="4"/>
     </row>
-    <row r="512" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G512" s="4"/>
     </row>
-    <row r="513" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G513" s="4"/>
     </row>
-    <row r="514" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G514" s="4"/>
     </row>
-    <row r="515" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G515" s="4"/>
     </row>
-    <row r="516" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G516" s="4"/>
     </row>
-    <row r="517" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G517" s="4"/>
     </row>
-    <row r="518" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G518" s="4"/>
     </row>
-    <row r="519" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G519" s="4"/>
     </row>
-    <row r="520" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G520" s="4"/>
     </row>
-    <row r="521" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G521" s="4"/>
     </row>
-    <row r="522" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G522" s="4"/>
     </row>
-    <row r="523" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G523" s="4"/>
     </row>
-    <row r="524" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G524" s="4"/>
     </row>
-    <row r="525" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G525" s="4"/>
     </row>
-    <row r="526" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G526" s="4"/>
     </row>
-    <row r="527" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G527" s="4"/>
     </row>
-    <row r="528" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G528" s="4"/>
     </row>
-    <row r="529" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G529" s="4"/>
     </row>
-    <row r="530" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G530" s="4"/>
     </row>
-    <row r="531" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G531" s="4"/>
     </row>
-    <row r="532" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G532" s="4"/>
     </row>
-    <row r="533" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G533" s="4"/>
     </row>
-    <row r="534" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G534" s="4"/>
     </row>
-    <row r="535" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G535" s="4"/>
     </row>
-    <row r="536" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G536" s="4"/>
     </row>
-    <row r="537" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G537" s="4"/>
     </row>
-    <row r="538" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G538" s="4"/>
     </row>
-    <row r="539" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G539" s="4"/>
     </row>
-    <row r="540" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G540" s="4"/>
     </row>
-    <row r="541" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G541" s="4"/>
     </row>
-    <row r="542" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G542" s="4"/>
     </row>
-    <row r="543" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G543" s="4"/>
     </row>
-    <row r="544" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G544" s="4"/>
     </row>
-    <row r="545" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G545" s="4"/>
     </row>
-    <row r="546" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G546" s="4"/>
     </row>
-    <row r="547" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G547" s="4"/>
     </row>
-    <row r="548" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G548" s="4"/>
     </row>
-    <row r="549" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G549" s="4"/>
     </row>
-    <row r="550" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G550" s="4"/>
     </row>
-    <row r="551" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G551" s="4"/>
     </row>
-    <row r="552" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G552" s="4"/>
     </row>
-    <row r="553" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G553" s="4"/>
     </row>
-    <row r="554" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G554" s="4"/>
     </row>
-    <row r="555" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G555" s="4"/>
     </row>
-    <row r="556" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G556" s="4"/>
     </row>
-    <row r="557" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G557" s="4"/>
     </row>
-    <row r="558" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G558" s="4"/>
     </row>
-    <row r="559" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G559" s="4"/>
     </row>
-    <row r="560" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G560" s="4"/>
     </row>
-    <row r="561" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G561" s="4"/>
     </row>
-    <row r="562" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G562" s="4"/>
     </row>
-    <row r="563" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G563" s="4"/>
     </row>
-    <row r="564" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G564" s="4"/>
     </row>
-    <row r="565" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G565" s="4"/>
     </row>
-    <row r="566" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G566" s="4"/>
     </row>
-    <row r="567" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G567" s="4"/>
     </row>
-    <row r="568" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G568" s="4"/>
     </row>
-    <row r="569" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G569" s="4"/>
     </row>
-    <row r="570" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G570" s="4"/>
     </row>
-    <row r="571" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G571" s="4"/>
     </row>
-    <row r="572" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G572" s="4"/>
     </row>
-    <row r="573" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G573" s="4"/>
     </row>
-    <row r="574" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G574" s="4"/>
     </row>
-    <row r="575" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G575" s="4"/>
     </row>
-    <row r="576" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G576" s="4"/>
     </row>
-    <row r="577" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G577" s="4"/>
     </row>
-    <row r="578" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G578" s="4"/>
     </row>
-    <row r="579" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G579" s="4"/>
     </row>
-    <row r="580" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G580" s="4"/>
     </row>
-    <row r="581" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G581" s="4"/>
     </row>
-    <row r="582" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G582" s="4"/>
     </row>
-    <row r="583" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G583" s="4"/>
     </row>
-    <row r="584" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G584" s="4"/>
     </row>
-    <row r="585" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G585" s="4"/>
     </row>
-    <row r="586" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G586" s="4"/>
     </row>
-    <row r="587" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G587" s="4"/>
     </row>
-    <row r="588" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G588" s="4"/>
     </row>
-    <row r="589" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G589" s="4"/>
     </row>
-    <row r="590" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G590" s="4"/>
     </row>
-    <row r="591" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G591" s="4"/>
     </row>
-    <row r="592" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G592" s="4"/>
     </row>
-    <row r="593" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G593" s="4"/>
     </row>
-    <row r="594" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G594" s="4"/>
     </row>
-    <row r="595" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G595" s="4"/>
     </row>
-    <row r="596" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G596" s="4"/>
     </row>
-    <row r="597" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G597" s="4"/>
     </row>
-    <row r="598" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G598" s="4"/>
     </row>
-    <row r="599" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G599" s="4"/>
     </row>
-    <row r="600" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G600" s="4"/>
     </row>
-    <row r="601" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G601" s="4"/>
     </row>
-    <row r="602" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G602" s="4"/>
     </row>
-    <row r="603" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G603" s="4"/>
     </row>
-    <row r="604" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G604" s="4"/>
     </row>
-    <row r="605" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G605" s="4"/>
     </row>
-    <row r="606" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G606" s="4"/>
     </row>
-    <row r="607" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G607" s="4"/>
     </row>
-    <row r="608" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G608" s="4"/>
     </row>
-    <row r="609" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G609" s="4"/>
     </row>
-    <row r="610" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G610" s="4"/>
     </row>
-    <row r="611" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G611" s="4"/>
     </row>
-    <row r="612" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G612" s="4"/>
     </row>
-    <row r="613" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G613" s="4"/>
     </row>
-    <row r="614" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G614" s="4"/>
     </row>
-    <row r="615" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G615" s="4"/>
     </row>
-    <row r="616" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G616" s="4"/>
     </row>
-    <row r="617" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G617" s="4"/>
     </row>
-    <row r="618" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G618" s="4"/>
     </row>
-    <row r="619" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G619" s="4"/>
     </row>
-    <row r="620" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G620" s="4"/>
     </row>
-    <row r="621" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G621" s="4"/>
     </row>
-    <row r="622" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G622" s="4"/>
     </row>
-    <row r="623" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G623" s="4"/>
     </row>
-    <row r="624" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G624" s="4"/>
     </row>
-    <row r="625" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G625" s="4"/>
     </row>
-    <row r="626" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G626" s="4"/>
     </row>
-    <row r="627" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G627" s="4"/>
     </row>
-    <row r="628" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G628" s="4"/>
     </row>
-    <row r="629" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G629" s="4"/>
     </row>
-    <row r="630" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G630" s="4"/>
     </row>
-    <row r="631" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G631" s="4"/>
     </row>
-    <row r="632" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G632" s="4"/>
     </row>
-    <row r="633" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G633" s="4"/>
     </row>
-    <row r="634" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G634" s="4"/>
     </row>
-    <row r="635" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G635" s="4"/>
     </row>
-    <row r="636" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G636" s="4"/>
     </row>
-    <row r="637" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G637" s="4"/>
     </row>
-    <row r="638" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G638" s="4"/>
     </row>
-    <row r="639" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G639" s="4"/>
     </row>
-    <row r="640" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="640" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G640" s="4"/>
     </row>
-    <row r="641" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="641" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G641" s="4"/>
     </row>
-    <row r="642" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G642" s="4"/>
     </row>
-    <row r="643" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G643" s="4"/>
     </row>
-    <row r="644" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G644" s="4"/>
     </row>
-    <row r="645" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G645" s="4"/>
     </row>
-    <row r="646" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G646" s="4"/>
     </row>
-    <row r="647" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G647" s="4"/>
     </row>
-    <row r="648" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G648" s="4"/>
     </row>
-    <row r="649" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="649" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G649" s="4"/>
     </row>
-    <row r="650" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="650" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G650" s="4"/>
     </row>
-    <row r="651" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="651" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G651" s="4"/>
     </row>
-    <row r="652" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="652" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G652" s="4"/>
     </row>
-    <row r="653" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="653" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G653" s="4"/>
     </row>
-    <row r="654" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="654" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G654" s="4"/>
     </row>
-    <row r="655" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="655" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G655" s="4"/>
     </row>
-    <row r="656" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="656" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G656" s="4"/>
     </row>
-    <row r="657" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="657" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G657" s="4"/>
     </row>
-    <row r="658" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="658" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G658" s="4"/>
     </row>
-    <row r="659" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="659" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G659" s="4"/>
     </row>
-    <row r="660" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="660" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G660" s="4"/>
     </row>
-    <row r="661" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="661" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G661" s="4"/>
     </row>
-    <row r="662" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="662" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G662" s="4"/>
     </row>
-    <row r="663" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="663" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G663" s="4"/>
     </row>
-    <row r="664" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="664" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G664" s="4"/>
     </row>
-    <row r="665" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="665" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G665" s="4"/>
     </row>
-    <row r="666" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="666" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G666" s="4"/>
     </row>
-    <row r="667" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="667" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G667" s="4"/>
     </row>
-    <row r="668" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="668" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G668" s="4"/>
     </row>
-    <row r="669" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="669" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G669" s="4"/>
     </row>
-    <row r="670" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="670" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G670" s="4"/>
     </row>
-    <row r="671" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="671" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G671" s="4"/>
     </row>
-    <row r="672" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="672" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G672" s="4"/>
     </row>
-    <row r="673" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="673" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G673" s="4"/>
     </row>
-    <row r="674" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="674" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G674" s="4"/>
     </row>
-    <row r="675" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G675" s="4"/>
     </row>
-    <row r="676" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G676" s="4"/>
     </row>
-    <row r="677" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G677" s="4"/>
     </row>
-    <row r="678" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="678" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G678" s="4"/>
     </row>
-    <row r="679" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="679" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G679" s="4"/>
     </row>
-    <row r="680" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="680" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G680" s="4"/>
     </row>
-    <row r="681" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="681" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G681" s="4"/>
     </row>
-    <row r="682" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="682" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G682" s="4"/>
     </row>
-    <row r="683" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="683" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G683" s="4"/>
     </row>
-    <row r="684" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="684" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G684" s="4"/>
     </row>
-    <row r="685" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="685" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G685" s="4"/>
     </row>
-    <row r="686" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="686" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G686" s="4"/>
     </row>
-    <row r="687" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G687" s="4"/>
     </row>
-    <row r="688" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="688" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G688" s="4"/>
     </row>
-    <row r="689" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="689" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G689" s="4"/>
     </row>
-    <row r="690" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="690" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G690" s="4"/>
     </row>
-    <row r="691" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G691" s="4"/>
     </row>
-    <row r="692" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G692" s="4"/>
     </row>
-    <row r="693" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G693" s="4"/>
     </row>
-    <row r="694" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G694" s="4"/>
     </row>
-    <row r="695" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G695" s="4"/>
     </row>
-    <row r="696" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="696" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G696" s="4"/>
     </row>
-    <row r="697" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="697" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G697" s="4"/>
     </row>
-    <row r="698" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G698" s="4"/>
     </row>
-    <row r="699" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="699" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G699" s="4"/>
     </row>
-    <row r="700" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="700" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G700" s="4"/>
     </row>
-    <row r="701" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="701" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G701" s="4"/>
     </row>
-    <row r="702" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="702" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G702" s="4"/>
     </row>
-    <row r="703" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="703" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G703" s="4"/>
     </row>
-    <row r="704" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="704" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G704" s="4"/>
     </row>
-    <row r="705" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="705" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G705" s="4"/>
     </row>
-    <row r="706" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="706" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G706" s="4"/>
     </row>
-    <row r="707" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="707" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G707" s="4"/>
     </row>
-    <row r="708" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="708" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G708" s="4"/>
     </row>
-    <row r="709" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G709" s="4"/>
     </row>
-    <row r="710" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="710" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G710" s="4"/>
     </row>
-    <row r="711" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="711" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G711" s="4"/>
     </row>
-    <row r="712" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="712" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G712" s="4"/>
     </row>
-    <row r="713" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="713" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G713" s="4"/>
     </row>
-    <row r="714" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G714" s="4"/>
     </row>
-    <row r="715" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G715" s="4"/>
     </row>
-    <row r="716" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="716" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G716" s="4"/>
     </row>
-    <row r="717" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G717" s="4"/>
     </row>
-    <row r="718" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="718" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G718" s="4"/>
     </row>
-    <row r="719" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G719" s="4"/>
     </row>
-    <row r="720" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="720" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G720" s="4"/>
     </row>
-    <row r="721" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="721" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G721" s="4"/>
     </row>
-    <row r="722" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="722" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G722" s="4"/>
     </row>
-    <row r="723" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G723" s="4"/>
     </row>
-    <row r="724" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G724" s="4"/>
     </row>
-    <row r="725" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="725" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G725" s="4"/>
     </row>
-    <row r="726" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="726" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G726" s="4"/>
     </row>
-    <row r="727" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="727" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G727" s="4"/>
     </row>
-    <row r="728" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="728" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G728" s="4"/>
     </row>
-    <row r="729" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="729" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G729" s="4"/>
     </row>
-    <row r="730" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="730" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G730" s="4"/>
     </row>
-    <row r="731" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="731" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G731" s="4"/>
     </row>
-    <row r="732" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G732" s="4"/>
     </row>
-    <row r="733" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G733" s="4"/>
     </row>
-    <row r="734" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="734" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G734" s="4"/>
     </row>
-    <row r="735" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="735" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G735" s="4"/>
     </row>
-    <row r="736" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G736" s="4"/>
     </row>
-    <row r="737" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="737" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G737" s="4"/>
     </row>
-    <row r="738" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="738" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G738" s="4"/>
     </row>
-    <row r="739" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G739" s="4"/>
     </row>
-    <row r="740" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="740" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G740" s="4"/>
     </row>
-    <row r="741" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G741" s="4"/>
     </row>
-    <row r="742" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="742" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G742" s="4"/>
     </row>
-    <row r="743" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="743" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G743" s="4"/>
     </row>
-    <row r="744" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="744" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G744" s="4"/>
     </row>
-    <row r="745" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="745" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G745" s="4"/>
     </row>
-    <row r="746" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="746" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G746" s="4"/>
     </row>
-    <row r="747" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="747" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G747" s="4"/>
     </row>
-    <row r="748" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="748" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G748" s="4"/>
     </row>
-    <row r="749" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="749" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G749" s="4"/>
     </row>
-    <row r="750" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="750" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G750" s="4"/>
     </row>
-    <row r="751" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="751" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G751" s="4"/>
     </row>
-    <row r="752" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="752" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G752" s="4"/>
     </row>
-    <row r="753" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="753" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G753" s="4"/>
     </row>
-    <row r="754" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="754" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G754" s="4"/>
     </row>
-    <row r="755" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G755" s="4"/>
     </row>
-    <row r="756" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="756" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G756" s="4"/>
     </row>
-    <row r="757" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="757" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G757" s="4"/>
     </row>
-    <row r="758" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="758" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G758" s="4"/>
     </row>
-    <row r="759" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G759" s="4"/>
     </row>
-    <row r="760" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="760" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G760" s="4"/>
     </row>
-    <row r="761" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="761" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G761" s="4"/>
     </row>
-    <row r="762" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="762" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G762" s="4"/>
     </row>
-    <row r="763" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G763" s="4"/>
     </row>
-    <row r="764" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="764" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G764" s="4"/>
     </row>
-    <row r="765" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="765" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G765" s="4"/>
     </row>
-    <row r="766" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="766" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G766" s="4"/>
     </row>
-    <row r="767" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="767" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G767" s="4"/>
     </row>
-    <row r="768" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="768" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G768" s="4"/>
     </row>
-    <row r="769" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="769" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G769" s="4"/>
     </row>
-    <row r="770" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="770" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G770" s="4"/>
     </row>
-    <row r="771" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="771" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G771" s="4"/>
     </row>
-    <row r="772" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="772" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G772" s="4"/>
     </row>
-    <row r="773" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="773" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G773" s="4"/>
     </row>
-    <row r="774" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="774" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G774" s="4"/>
     </row>
-    <row r="775" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="775" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G775" s="4"/>
     </row>
-    <row r="776" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="776" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G776" s="4"/>
     </row>
-    <row r="777" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="777" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G777" s="4"/>
     </row>
-    <row r="778" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="778" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G778" s="4"/>
     </row>
-    <row r="779" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="779" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G779" s="4"/>
     </row>
-    <row r="780" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="780" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G780" s="4"/>
     </row>
-    <row r="781" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="781" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G781" s="4"/>
     </row>
-    <row r="782" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="782" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G782" s="4"/>
     </row>
-    <row r="783" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="783" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G783" s="4"/>
     </row>
-    <row r="784" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="784" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G784" s="4"/>
     </row>
-    <row r="785" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="785" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G785" s="4"/>
     </row>
-    <row r="786" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="786" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G786" s="4"/>
     </row>
-    <row r="787" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="787" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G787" s="4"/>
     </row>
-    <row r="788" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="788" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G788" s="4"/>
     </row>
-    <row r="789" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="789" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G789" s="4"/>
     </row>
-    <row r="790" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="790" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G790" s="4"/>
     </row>
-    <row r="791" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="791" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G791" s="4"/>
     </row>
-    <row r="792" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="792" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G792" s="4"/>
     </row>
-    <row r="793" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="793" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G793" s="4"/>
     </row>
-    <row r="794" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="794" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G794" s="4"/>
     </row>
-    <row r="795" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="795" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G795" s="4"/>
     </row>
-    <row r="796" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="796" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G796" s="4"/>
     </row>
-    <row r="797" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="797" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G797" s="4"/>
     </row>
-    <row r="798" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="798" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G798" s="4"/>
     </row>
-    <row r="799" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="799" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G799" s="4"/>
     </row>
-    <row r="800" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="800" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G800" s="4"/>
     </row>
-    <row r="801" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="801" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G801" s="4"/>
     </row>
-    <row r="802" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="802" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G802" s="4"/>
     </row>
-    <row r="803" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="803" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G803" s="4"/>
     </row>
-    <row r="804" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="804" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G804" s="4"/>
     </row>
-    <row r="805" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="805" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G805" s="4"/>
     </row>
-    <row r="806" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="806" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G806" s="4"/>
     </row>
-    <row r="807" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="807" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G807" s="4"/>
     </row>
-    <row r="808" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="808" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G808" s="4"/>
     </row>
-    <row r="809" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="809" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G809" s="4"/>
     </row>
-    <row r="810" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="810" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G810" s="4"/>
     </row>
-    <row r="811" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="811" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G811" s="4"/>
     </row>
-    <row r="812" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="812" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G812" s="4"/>
     </row>
-    <row r="813" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="813" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G813" s="4"/>
     </row>
-    <row r="814" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="814" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G814" s="4"/>
     </row>
-    <row r="815" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="815" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G815" s="4"/>
     </row>
-    <row r="816" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="816" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G816" s="4"/>
     </row>
-    <row r="817" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="817" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G817" s="4"/>
     </row>
-    <row r="818" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="818" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G818" s="4"/>
     </row>
-    <row r="819" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="819" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G819" s="4"/>
     </row>
-    <row r="820" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="820" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G820" s="4"/>
     </row>
-    <row r="821" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="821" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G821" s="4"/>
     </row>
-    <row r="822" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="822" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G822" s="4"/>
     </row>
-    <row r="823" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="823" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G823" s="4"/>
     </row>
-    <row r="824" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="824" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G824" s="4"/>
     </row>
-    <row r="825" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="825" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G825" s="4"/>
     </row>
-    <row r="826" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="826" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G826" s="4"/>
     </row>
-    <row r="827" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="827" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G827" s="4"/>
     </row>
-    <row r="828" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="828" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G828" s="4"/>
     </row>
-    <row r="829" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="829" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G829" s="4"/>
     </row>
-    <row r="830" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="830" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G830" s="4"/>
     </row>
-    <row r="831" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="831" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G831" s="4"/>
     </row>
-    <row r="832" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="832" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G832" s="4"/>
     </row>
-    <row r="833" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="833" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G833" s="4"/>
     </row>
-    <row r="834" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="834" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G834" s="4"/>
     </row>
-    <row r="835" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="835" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G835" s="4"/>
     </row>
-    <row r="836" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="836" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G836" s="4"/>
     </row>
-    <row r="837" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="837" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G837" s="4"/>
     </row>
-    <row r="838" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="838" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G838" s="4"/>
     </row>
-    <row r="839" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="839" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G839" s="4"/>
     </row>
-    <row r="840" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="840" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G840" s="4"/>
     </row>
-    <row r="841" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="841" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G841" s="4"/>
     </row>
-    <row r="842" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="842" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G842" s="4"/>
     </row>
-    <row r="843" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="843" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G843" s="4"/>
     </row>
-    <row r="844" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="844" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G844" s="4"/>
     </row>
-    <row r="845" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="845" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G845" s="4"/>
     </row>
-    <row r="846" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="846" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G846" s="4"/>
     </row>
-    <row r="847" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="847" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G847" s="4"/>
     </row>
-    <row r="848" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="848" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G848" s="4"/>
     </row>
-    <row r="849" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="849" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G849" s="4"/>
     </row>
-    <row r="850" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="850" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G850" s="4"/>
     </row>
-    <row r="851" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="851" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G851" s="4"/>
     </row>
-    <row r="852" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="852" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G852" s="4"/>
     </row>
-    <row r="853" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="853" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G853" s="4"/>
     </row>
-    <row r="854" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="854" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G854" s="4"/>
     </row>
-    <row r="855" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="855" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G855" s="4"/>
     </row>
-    <row r="856" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="856" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G856" s="4"/>
     </row>
-    <row r="857" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="857" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G857" s="4"/>
     </row>
-    <row r="858" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="858" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G858" s="4"/>
     </row>
-    <row r="859" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="859" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G859" s="4"/>
     </row>
-    <row r="860" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="860" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G860" s="4"/>
     </row>
-    <row r="861" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="861" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G861" s="4"/>
     </row>
-    <row r="862" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="862" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G862" s="4"/>
     </row>
-    <row r="863" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="863" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G863" s="4"/>
     </row>
-    <row r="864" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="864" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G864" s="4"/>
     </row>
-    <row r="865" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="865" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G865" s="4"/>
     </row>
-    <row r="866" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="866" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G866" s="4"/>
     </row>
-    <row r="867" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="867" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G867" s="4"/>
     </row>
-    <row r="868" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="868" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G868" s="4"/>
     </row>
-    <row r="869" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="869" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G869" s="4"/>
     </row>
-    <row r="870" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="870" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G870" s="4"/>
     </row>
-    <row r="871" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="871" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G871" s="4"/>
     </row>
-    <row r="872" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="872" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G872" s="4"/>
     </row>
-    <row r="873" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="873" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G873" s="4"/>
     </row>
-    <row r="874" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="874" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G874" s="4"/>
     </row>
-    <row r="875" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="875" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G875" s="4"/>
     </row>
-    <row r="876" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="876" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G876" s="4"/>
     </row>
-    <row r="877" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="877" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G877" s="4"/>
     </row>
-    <row r="878" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="878" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G878" s="4"/>
     </row>
-    <row r="879" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="879" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G879" s="4"/>
     </row>
-    <row r="880" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="880" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G880" s="4"/>
     </row>
-    <row r="881" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="881" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G881" s="4"/>
     </row>
-    <row r="882" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="882" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G882" s="4"/>
     </row>
-    <row r="883" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="883" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G883" s="4"/>
     </row>
-    <row r="884" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="884" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G884" s="4"/>
     </row>
-    <row r="885" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="885" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G885" s="4"/>
     </row>
-    <row r="886" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="886" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G886" s="4"/>
     </row>
-    <row r="887" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="887" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G887" s="4"/>
     </row>
-    <row r="888" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="888" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G888" s="4"/>
     </row>
-    <row r="889" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="889" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G889" s="4"/>
     </row>
-    <row r="890" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="890" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G890" s="4"/>
     </row>
-    <row r="891" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="891" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G891" s="4"/>
     </row>
-    <row r="892" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="892" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G892" s="4"/>
     </row>
-    <row r="893" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="893" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G893" s="4"/>
     </row>
-    <row r="894" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="894" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G894" s="4"/>
     </row>
-    <row r="895" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="895" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G895" s="4"/>
     </row>
-    <row r="896" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="896" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G896" s="4"/>
     </row>
-    <row r="897" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="897" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G897" s="4"/>
     </row>
-    <row r="898" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="898" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G898" s="4"/>
     </row>
-    <row r="899" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="899" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G899" s="4"/>
     </row>
-    <row r="900" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="900" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G900" s="4"/>
     </row>
-    <row r="901" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="901" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G901" s="4"/>
     </row>
-    <row r="902" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="902" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G902" s="4"/>
     </row>
-    <row r="903" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="903" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G903" s="4"/>
     </row>
-    <row r="904" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="904" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G904" s="4"/>
     </row>
-    <row r="905" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="905" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G905" s="4"/>
     </row>
-    <row r="906" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="906" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G906" s="4"/>
     </row>
-    <row r="907" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="907" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G907" s="4"/>
     </row>
-    <row r="908" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="908" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G908" s="4"/>
     </row>
-    <row r="909" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="909" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G909" s="4"/>
     </row>
-    <row r="910" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="910" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G910" s="4"/>
     </row>
-    <row r="911" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="911" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G911" s="4"/>
     </row>
-    <row r="912" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="912" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G912" s="4"/>
     </row>
-    <row r="913" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="913" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G913" s="4"/>
     </row>
-    <row r="914" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="914" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G914" s="4"/>
     </row>
-    <row r="915" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="915" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G915" s="4"/>
     </row>
-    <row r="916" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="916" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G916" s="4"/>
     </row>
-    <row r="917" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="917" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G917" s="4"/>
     </row>
-    <row r="918" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="918" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G918" s="4"/>
     </row>
-    <row r="919" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="919" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G919" s="4"/>
     </row>
-    <row r="920" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="920" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G920" s="4"/>
     </row>
-    <row r="921" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="921" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G921" s="4"/>
     </row>
-    <row r="922" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="922" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G922" s="4"/>
     </row>
-    <row r="923" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="923" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G923" s="4"/>
     </row>
-    <row r="924" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="924" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G924" s="4"/>
     </row>
-    <row r="925" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="925" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G925" s="4"/>
     </row>
-    <row r="926" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="926" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G926" s="4"/>
     </row>
-    <row r="927" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="927" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G927" s="4"/>
     </row>
-    <row r="928" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="928" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G928" s="4"/>
     </row>
-    <row r="929" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="929" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G929" s="4"/>
     </row>
-    <row r="930" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="930" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G930" s="4"/>
     </row>
-    <row r="931" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="931" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G931" s="4"/>
     </row>
-    <row r="932" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="932" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G932" s="4"/>
     </row>
-    <row r="933" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="933" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G933" s="4"/>
     </row>
-    <row r="934" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="934" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G934" s="4"/>
     </row>
-    <row r="935" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="935" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G935" s="4"/>
     </row>
-    <row r="936" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="936" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G936" s="4"/>
     </row>
-    <row r="937" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="937" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G937" s="4"/>
     </row>
-    <row r="938" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="938" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G938" s="4"/>
     </row>
-    <row r="939" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="939" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G939" s="4"/>
     </row>
-    <row r="940" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="940" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G940" s="4"/>
     </row>
-    <row r="941" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="941" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G941" s="4"/>
     </row>
-    <row r="942" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="942" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G942" s="4"/>
     </row>
-    <row r="943" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="943" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G943" s="4"/>
     </row>
-    <row r="944" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="944" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G944" s="4"/>
     </row>
-    <row r="945" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="945" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G945" s="4"/>
     </row>
-    <row r="946" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="946" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G946" s="4"/>
     </row>
-    <row r="947" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="947" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G947" s="4"/>
     </row>
-    <row r="948" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="948" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G948" s="4"/>
     </row>
-    <row r="949" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="949" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G949" s="4"/>
     </row>
-    <row r="950" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="950" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G950" s="4"/>
     </row>
-    <row r="951" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="951" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G951" s="4"/>
     </row>
-    <row r="952" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="952" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G952" s="4"/>
     </row>
-    <row r="953" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="953" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G953" s="4"/>
     </row>
-    <row r="954" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="954" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G954" s="4"/>
     </row>
-    <row r="955" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="955" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G955" s="4"/>
     </row>
-    <row r="956" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="956" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G956" s="4"/>
     </row>
-    <row r="957" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="957" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G957" s="4"/>
     </row>
-    <row r="958" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="958" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G958" s="4"/>
     </row>
-    <row r="959" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="959" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G959" s="4"/>
     </row>
-    <row r="960" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="960" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G960" s="4"/>
     </row>
-    <row r="961" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="961" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G961" s="4"/>
     </row>
-    <row r="962" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="962" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G962" s="4"/>
     </row>
-    <row r="963" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="963" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G963" s="4"/>
     </row>
-    <row r="964" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="964" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G964" s="4"/>
     </row>
-    <row r="965" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="965" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G965" s="4"/>
     </row>
-    <row r="966" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="966" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G966" s="4"/>
     </row>
-    <row r="967" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="967" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G967" s="4"/>
     </row>
-    <row r="968" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="968" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G968" s="4"/>
     </row>
-    <row r="969" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="969" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G969" s="4"/>
     </row>
-    <row r="970" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="970" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G970" s="4"/>
     </row>
-    <row r="971" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="971" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G971" s="4"/>
     </row>
-    <row r="972" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="972" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G972" s="4"/>
     </row>
-    <row r="973" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="973" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G973" s="4"/>
     </row>
-    <row r="974" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="974" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G974" s="4"/>
     </row>
-    <row r="975" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="975" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G975" s="4"/>
     </row>
-    <row r="976" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="976" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G976" s="4"/>
     </row>
-    <row r="977" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="977" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G977" s="4"/>
     </row>
-    <row r="978" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="978" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G978" s="4"/>
     </row>
-    <row r="979" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="979" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G979" s="4"/>
     </row>
-    <row r="980" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="980" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G980" s="4"/>
     </row>
-    <row r="981" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="981" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G981" s="4"/>
     </row>
-    <row r="982" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="982" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G982" s="4"/>
     </row>
-    <row r="983" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="983" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G983" s="4"/>
     </row>
-    <row r="984" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="984" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G984" s="4"/>
     </row>
-    <row r="985" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="985" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G985" s="4"/>
     </row>
-    <row r="986" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="986" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G986" s="4"/>
     </row>
-    <row r="987" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="987" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G987" s="4"/>
     </row>
-    <row r="988" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="988" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G988" s="4"/>
     </row>
-    <row r="989" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="989" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G989" s="4"/>
     </row>
-    <row r="990" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="990" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G990" s="4"/>
     </row>
-    <row r="991" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="991" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G991" s="4"/>
     </row>
-    <row r="992" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="992" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G992" s="4"/>
     </row>
-    <row r="993" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="993" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G993" s="4"/>
     </row>
-    <row r="994" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="994" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G994" s="4"/>
     </row>
-    <row r="995" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="995" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G995" s="4"/>
     </row>
-    <row r="996" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="996" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G996" s="4"/>
     </row>
-    <row r="997" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="997" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G997" s="4"/>
     </row>
-    <row r="998" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="998" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G998" s="4"/>
     </row>
-    <row r="999" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="999" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G999" s="4"/>
     </row>
-    <row r="1000" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1000" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G1000" s="4"/>
     </row>
-    <row r="1001" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="1001" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G1001" s="4"/>
     </row>
-    <row r="1002" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1002" s="4"/>
-    </row>
-    <row r="1003" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1003" s="4"/>
-    </row>
-    <row r="1004" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1004" s="4"/>
-    </row>
-    <row r="1005" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1005" s="4"/>
-    </row>
-    <row r="1006" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1006" s="4"/>
-    </row>
-    <row r="1007" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1007" s="4"/>
-    </row>
-    <row r="1008" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1008" s="4"/>
-    </row>
-    <row r="1009" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1009" s="4"/>
-    </row>
-    <row r="1010" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1010" s="4"/>
-    </row>
-    <row r="1011" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1011" s="4"/>
-    </row>
-    <row r="1012" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1012" s="4"/>
-    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="Please select a valid role " errorStyle="stop" errorTitle="Roles Error" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G1:G1001" type="list">
+      <formula1>Presets!$I$2:$I$25</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Roles Error" error="Please select a valid role " xr:uid="{00000000-0002-0000-0200-000000000000}">
-          <x14:formula1>
-            <xm:f>Presets!$I$2:$I$25</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>G1:G1013</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="38" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="28" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4"/>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.5703125" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="50.57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H121"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28" style="6" customWidth="1"/>
-    <col min="4" max="16384" width="11.5703125" style="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="19.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="28"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="6" width="11.57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -4044,7 +4088,7 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -4054,7 +4098,7 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -4064,7 +4108,7 @@
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -4074,7 +4118,7 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -4084,7 +4128,7 @@
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -4094,7 +4138,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -4104,7 +4148,7 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -4114,7 +4158,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -4124,7 +4168,7 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -4134,7 +4178,7 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -4144,7 +4188,7 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -4154,7 +4198,7 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -4164,7 +4208,7 @@
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -4174,7 +4218,7 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -4184,7 +4228,7 @@
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -4194,7 +4238,7 @@
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -4204,7 +4248,7 @@
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -4214,7 +4258,7 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -4224,7 +4268,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -4234,7 +4278,7 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -4244,7 +4288,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -4254,7 +4298,7 @@
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -4264,7 +4308,7 @@
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -4274,7 +4318,7 @@
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -4284,7 +4328,7 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -4294,7 +4338,7 @@
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -4304,7 +4348,7 @@
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -4314,7 +4358,7 @@
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -4324,7 +4368,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -4334,7 +4378,7 @@
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -4344,7 +4388,7 @@
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -4354,7 +4398,7 @@
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
@@ -4364,7 +4408,7 @@
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -4374,7 +4418,7 @@
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -4384,7 +4428,7 @@
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -4394,7 +4438,7 @@
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -4404,7 +4448,7 @@
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -4414,7 +4458,7 @@
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -4424,7 +4468,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -4434,7 +4478,7 @@
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -4444,7 +4488,7 @@
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -4454,7 +4498,7 @@
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -4464,7 +4508,7 @@
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -4474,7 +4518,7 @@
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -4484,7 +4528,7 @@
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -4494,7 +4538,7 @@
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -4504,7 +4548,7 @@
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -4514,7 +4558,7 @@
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -4524,7 +4568,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -4534,7 +4578,7 @@
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -4544,7 +4588,7 @@
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -4554,7 +4598,7 @@
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -4564,7 +4608,7 @@
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -4574,7 +4618,7 @@
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -4584,7 +4628,7 @@
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
@@ -4594,7 +4638,7 @@
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -4604,7 +4648,7 @@
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -4614,7 +4658,7 @@
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -4624,7 +4668,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -4634,7 +4678,7 @@
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -4644,7 +4688,7 @@
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
@@ -4654,7 +4698,7 @@
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -4664,7 +4708,7 @@
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -4674,7 +4718,7 @@
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -4684,7 +4728,7 @@
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="7"/>
@@ -4694,7 +4738,7 @@
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="7"/>
@@ -4704,7 +4748,7 @@
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="7"/>
@@ -4714,7 +4758,7 @@
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="7"/>
@@ -4724,7 +4768,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
@@ -4734,7 +4778,7 @@
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
@@ -4744,7 +4788,7 @@
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -4754,7 +4798,7 @@
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -4764,7 +4808,7 @@
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -4774,7 +4818,7 @@
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
@@ -4784,7 +4828,7 @@
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
@@ -4794,7 +4838,7 @@
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
@@ -4804,7 +4848,7 @@
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -4814,7 +4858,7 @@
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -4824,7 +4868,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
@@ -4834,7 +4878,7 @@
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
@@ -4844,7 +4888,7 @@
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
@@ -4854,7 +4898,7 @@
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -4864,7 +4908,7 @@
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
@@ -4874,7 +4918,7 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -4884,7 +4928,7 @@
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
@@ -4894,7 +4938,7 @@
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
@@ -4904,7 +4948,7 @@
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
@@ -4914,7 +4958,7 @@
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -4924,7 +4968,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
@@ -4934,7 +4978,7 @@
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
@@ -4944,7 +4988,7 @@
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
@@ -4954,7 +4998,7 @@
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
@@ -4964,7 +5008,7 @@
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
@@ -4974,7 +5018,7 @@
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
@@ -4984,7 +5028,7 @@
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
@@ -4994,7 +5038,7 @@
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
@@ -5004,7 +5048,7 @@
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
@@ -5014,7 +5058,7 @@
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
@@ -5024,7 +5068,7 @@
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
       <c r="C101" s="7"/>
@@ -5034,7 +5078,7 @@
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
       <c r="C102" s="7"/>
@@ -5044,7 +5088,7 @@
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
@@ -5054,7 +5098,7 @@
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
@@ -5064,7 +5108,7 @@
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
@@ -5074,7 +5118,7 @@
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
@@ -5084,7 +5128,7 @@
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
@@ -5094,7 +5138,7 @@
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
@@ -5104,7 +5148,7 @@
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
@@ -5114,7 +5158,7 @@
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
@@ -5124,7 +5168,7 @@
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
@@ -5134,7 +5178,7 @@
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -5144,7 +5188,7 @@
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
@@ -5154,7 +5198,7 @@
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
@@ -5164,7 +5208,7 @@
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
@@ -5174,7 +5218,7 @@
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
@@ -5184,7 +5228,7 @@
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
@@ -5194,7 +5238,7 @@
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
@@ -5204,7 +5248,7 @@
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
@@ -5214,7 +5258,7 @@
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
@@ -5224,7 +5268,7 @@
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
@@ -5235,9 +5279,10 @@
       <c r="H121" s="7"/>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
@@ -5245,320 +5290,283 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21.140625" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="8" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="G4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="I4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="8" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="37.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="27" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="4" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="4" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="G7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="4" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="I11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="4" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="4" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="I14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="4" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="I16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="4" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="I17" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="I18" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="I19" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I20" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I21" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I22" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I23" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I24" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I25" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Roles Error" error="Please select a valid role " sqref="G1:G1025" xr:uid="{00000000-0002-0000-0800-000000000000}">
+    <dataValidation allowBlank="true" error="Please select a valid role " errorStyle="stop" errorTitle="Roles Error" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G1:G1025" type="list">
       <formula1>$I$2:$I$25</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <tableParts count="4">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>

--- a/auto_repair/public/www/assets/xlsx/si-6.xlsx
+++ b/auto_repair/public/www/assets/xlsx/si-6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abees\Documents\sic\auto-repair-erp\web\src\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CB0A61-8F2A-4D4B-A538-A6250C32FC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15BFA07-2AFD-45E6-BDDD-2C1A998743FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="8" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiscal Years" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Assets" sheetId="11" r:id="rId11"/>
     <sheet name="Customers" sheetId="12" r:id="rId12"/>
     <sheet name="Suppliers" sheetId="13" r:id="rId13"/>
-    <sheet name="Invoices" sheetId="14" r:id="rId14"/>
+    <sheet name="Invoices" sheetId="20" r:id="rId14"/>
     <sheet name="Presets" sheetId="15" r:id="rId15"/>
     <sheet name="Sheet1" sheetId="19" r:id="rId16"/>
   </sheets>
@@ -35,7 +35,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Products!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Raw Material'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Trading!$A$1:$G$1</definedName>
-    <definedName name="arial">Invoices!$1:$1048576</definedName>
+    <definedName name="arial" localSheetId="13">Invoices!$1:$1048576</definedName>
+    <definedName name="arial">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="124">
   <si>
     <t>year</t>
   </si>
@@ -184,9 +185,6 @@
     <t>due_date</t>
   </si>
   <si>
-    <t>outstanding_amount</t>
-  </si>
-  <si>
     <t>Types</t>
   </si>
   <si>
@@ -373,21 +371,6 @@
     <t>administrator</t>
   </si>
   <si>
-    <t>Strategy</t>
-  </si>
-  <si>
-    <t>Innovation</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Production</t>
-  </si>
-  <si>
     <t>Support</t>
   </si>
   <si>
@@ -437,6 +420,15 @@
   </si>
   <si>
     <t>Mobile Number</t>
+  </si>
+  <si>
+    <t>paid_amount</t>
+  </si>
+  <si>
+    <t>grand_total</t>
+  </si>
+  <si>
+    <t>system</t>
   </si>
 </sst>
 </file>
@@ -961,31 +953,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C1" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E1" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1061,13 +1053,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1114,18 +1106,19 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:E1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5972704F-1DBA-48AA-A0F4-17718DAC9EAD}">
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="16" customWidth="1"/>
+    <col min="1" max="1" width="40.109375" style="16" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" style="16" customWidth="1"/>
     <col min="3" max="4" width="19.6640625" style="17" customWidth="1"/>
     <col min="5" max="5" width="35.88671875" style="18" customWidth="1"/>
-    <col min="6" max="16384" width="11.5546875" style="16"/>
+    <col min="6" max="6" width="18.21875" style="16" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="16" t="s">
         <v>40</v>
       </c>
@@ -1139,7 +1132,10 @@
         <v>41</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>42</v>
+        <v>122</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1163,27 +1159,27 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1">
       <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>44</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>46</v>
-      </c>
-      <c r="I1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="18.75" customHeight="1">
       <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -1192,24 +1188,24 @@
         <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="18.75" customHeight="1">
       <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
         <v>51</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>53</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>54</v>
-      </c>
-      <c r="I3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18.75" customHeight="1">
@@ -1217,199 +1213,199 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
         <v>56</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>57</v>
-      </c>
-      <c r="I4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18.75" customHeight="1">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" t="s">
         <v>59</v>
-      </c>
-      <c r="I5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18.75" customHeight="1">
       <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
         <v>61</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>62</v>
-      </c>
-      <c r="I6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18.75" customHeight="1">
       <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" t="s">
         <v>64</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>65</v>
-      </c>
-      <c r="I7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18.75" customHeight="1">
       <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" t="s">
         <v>67</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>68</v>
-      </c>
-      <c r="I8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18.75" customHeight="1">
       <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" t="s">
         <v>70</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>71</v>
-      </c>
-      <c r="I9" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18.75" customHeight="1">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18.75" customHeight="1">
       <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
         <v>75</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>76</v>
-      </c>
-      <c r="I11" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18.75" customHeight="1">
       <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s">
         <v>78</v>
-      </c>
-      <c r="I12" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18.75" customHeight="1">
       <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" t="s">
         <v>80</v>
-      </c>
-      <c r="I13" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18.75" customHeight="1">
       <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" t="s">
         <v>82</v>
-      </c>
-      <c r="I14" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18.75" customHeight="1">
       <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" t="s">
         <v>84</v>
-      </c>
-      <c r="I15" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18.75" customHeight="1">
       <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="I16" t="s">
         <v>86</v>
-      </c>
-      <c r="I16" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18.75" customHeight="1">
       <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" t="s">
         <v>88</v>
-      </c>
-      <c r="I17" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="18.75" customHeight="1">
       <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" t="s">
         <v>90</v>
-      </c>
-      <c r="I18" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="18.75" customHeight="1">
       <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" t="s">
         <v>92</v>
-      </c>
-      <c r="I19" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="18.75" customHeight="1">
       <c r="A20" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" t="s">
         <v>94</v>
-      </c>
-      <c r="I20" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="18.75" customHeight="1">
       <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="I21" t="s">
         <v>96</v>
-      </c>
-      <c r="I21" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1">
       <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="I22" t="s">
         <v>98</v>
-      </c>
-      <c r="I22" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="18.75" customHeight="1">
       <c r="A23" t="s">
+        <v>99</v>
+      </c>
+      <c r="I23" t="s">
         <v>100</v>
-      </c>
-      <c r="I23" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18.75" customHeight="1">
       <c r="A24" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" t="s">
         <v>102</v>
-      </c>
-      <c r="I24" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="I25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1519,45 +1515,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="30.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>110</v>
+      <c r="B1" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -1625,10 +1595,10 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
@@ -1644,10 +1614,10 @@
         <v>12345672@mail.com</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I2" t="s">
         <v>6</v>
@@ -1770,28 +1740,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="21" t="s">
         <v>113</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1824,28 +1794,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="21" t="s">
         <v>113</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="H1" s="21" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1878,37 +1848,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C1" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:11">

--- a/auto_repair/public/www/assets/xlsx/si-6.xlsx
+++ b/auto_repair/public/www/assets/xlsx/si-6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abees\Documents\sic\auto-repair-erp\web\src\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15BFA07-2AFD-45E6-BDDD-2C1A998743FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656B2AB4-843D-46E1-91CF-15469E79002C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiscal Years" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Journal Entries'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Products!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Raw Material'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Trading!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Products!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Raw Material'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Trading!$A$1:$H$1</definedName>
     <definedName name="arial" localSheetId="13">Invoices!$1:$1048576</definedName>
     <definedName name="arial">#REF!</definedName>
   </definedNames>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="125">
   <si>
     <t>year</t>
   </si>
@@ -429,6 +429,9 @@
   </si>
   <si>
     <t>system</t>
+  </si>
+  <si>
+    <t>Is Recycable</t>
   </si>
 </sst>
 </file>
@@ -1723,22 +1726,23 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD83FC68-3866-4B53-B82D-AC812A1EEF62}">
-  <dimension ref="A1:XFA1"/>
+  <dimension ref="A1:XFB1"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="25.33203125" style="13" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" style="20" customWidth="1"/>
     <col min="3" max="3" width="36.88671875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="17" style="13" customWidth="1"/>
-    <col min="8" max="8" width="21.33203125" style="21" customWidth="1"/>
-    <col min="9" max="16381" width="11.5546875" style="13"/>
-    <col min="16382" max="16384" width="11.5546875" style="14"/>
+    <col min="4" max="4" width="17.6640625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="17" style="13" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" style="21" customWidth="1"/>
+    <col min="10" max="16382" width="11.5546875" style="13"/>
+    <col min="16383" max="16384" width="11.5546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="15" t="s">
         <v>116</v>
       </c>
@@ -1749,18 +1753,21 @@
         <v>106</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1777,22 +1784,23 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE5D49AE-AF0F-4668-A81E-764A0CB4B708}">
-  <dimension ref="A1:XFA1"/>
+  <dimension ref="A1:XFB1"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="28.109375" style="13" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" style="20" customWidth="1"/>
     <col min="3" max="3" width="36.88671875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="17" style="13" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" style="21" customWidth="1"/>
-    <col min="9" max="16381" width="11.5546875" style="13"/>
-    <col min="16382" max="16384" width="11.5546875" style="14"/>
+    <col min="4" max="4" width="15.33203125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="17" style="13" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" style="21" customWidth="1"/>
+    <col min="10" max="16382" width="11.5546875" style="13"/>
+    <col min="16383" max="16384" width="11.5546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="15" t="s">
         <v>116</v>
       </c>
@@ -1803,18 +1811,21 @@
         <v>106</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="21" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1830,23 +1841,23 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:XFB6"/>
+  <dimension ref="A1:XFC6"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="13" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.33203125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="21" customWidth="1"/>
-    <col min="8" max="8" width="22.44140625" style="13" customWidth="1"/>
-    <col min="9" max="9" width="24" style="13" customWidth="1"/>
-    <col min="10" max="11" width="22.33203125" style="13" customWidth="1"/>
-    <col min="13" max="16382" width="11.5546875" style="13"/>
-    <col min="16383" max="16384" width="11.5546875" style="14"/>
+    <col min="3" max="4" width="18.88671875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.33203125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" style="21" customWidth="1"/>
+    <col min="9" max="9" width="22.44140625" style="13" customWidth="1"/>
+    <col min="10" max="10" width="24" style="13" customWidth="1"/>
+    <col min="11" max="12" width="22.33203125" style="13" customWidth="1"/>
+    <col min="14" max="16383" width="11.5546875" style="13"/>
+    <col min="16384" max="16384" width="11.5546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="15" t="s">
         <v>116</v>
       </c>
@@ -1857,39 +1868,43 @@
         <v>106</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" s="15"/>
       <c r="B6" s="19"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="G6" s="15"/>
       <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/auto_repair/public/www/assets/xlsx/si-6.xlsx
+++ b/auto_repair/public/www/assets/xlsx/si-6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abees\Documents\sic\auto-repair-erp\web\src\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656B2AB4-843D-46E1-91CF-15469E79002C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15BFA07-2AFD-45E6-BDDD-2C1A998743FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiscal Years" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Journal Entries'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Products!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Raw Material'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Trading!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Products!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Raw Material'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Trading!$A$1:$G$1</definedName>
     <definedName name="arial" localSheetId="13">Invoices!$1:$1048576</definedName>
     <definedName name="arial">#REF!</definedName>
   </definedNames>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="124">
   <si>
     <t>year</t>
   </si>
@@ -429,9 +429,6 @@
   </si>
   <si>
     <t>system</t>
-  </si>
-  <si>
-    <t>Is Recycable</t>
   </si>
 </sst>
 </file>
@@ -1726,23 +1723,22 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD83FC68-3866-4B53-B82D-AC812A1EEF62}">
-  <dimension ref="A1:XFB1"/>
+  <dimension ref="A1:XFA1"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="25.33203125" style="13" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" style="20" customWidth="1"/>
     <col min="3" max="3" width="36.88671875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="13" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" style="13" customWidth="1"/>
-    <col min="8" max="8" width="17" style="13" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="21" customWidth="1"/>
-    <col min="10" max="16382" width="11.5546875" style="13"/>
-    <col min="16383" max="16384" width="11.5546875" style="14"/>
+    <col min="4" max="4" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="17" style="13" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" style="21" customWidth="1"/>
+    <col min="9" max="16381" width="11.5546875" style="13"/>
+    <col min="16382" max="16384" width="11.5546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="15" t="s">
         <v>116</v>
       </c>
@@ -1753,21 +1749,18 @@
         <v>106</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1784,23 +1777,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE5D49AE-AF0F-4668-A81E-764A0CB4B708}">
-  <dimension ref="A1:XFB1"/>
+  <dimension ref="A1:XFA1"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="28.109375" style="13" customWidth="1"/>
     <col min="2" max="2" width="24.33203125" style="20" customWidth="1"/>
     <col min="3" max="3" width="36.88671875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" style="13" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" style="13" customWidth="1"/>
-    <col min="8" max="8" width="17" style="13" customWidth="1"/>
-    <col min="9" max="9" width="21.6640625" style="21" customWidth="1"/>
-    <col min="10" max="16382" width="11.5546875" style="13"/>
-    <col min="16383" max="16384" width="11.5546875" style="14"/>
+    <col min="4" max="4" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="13" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="17" style="13" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" style="21" customWidth="1"/>
+    <col min="9" max="16381" width="11.5546875" style="13"/>
+    <col min="16382" max="16384" width="11.5546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="15" t="s">
         <v>116</v>
       </c>
@@ -1811,21 +1803,18 @@
         <v>106</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1841,23 +1830,23 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:XFC6"/>
+  <dimension ref="A1:XFB6"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="13" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" style="20" customWidth="1"/>
-    <col min="3" max="4" width="18.88671875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="17.33203125" style="13" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="22.44140625" style="13" customWidth="1"/>
-    <col min="10" max="10" width="24" style="13" customWidth="1"/>
-    <col min="11" max="12" width="22.33203125" style="13" customWidth="1"/>
-    <col min="14" max="16383" width="11.5546875" style="13"/>
-    <col min="16384" max="16384" width="11.5546875" style="14"/>
+    <col min="3" max="3" width="18.88671875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17.33203125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="22.44140625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="24" style="13" customWidth="1"/>
+    <col min="10" max="11" width="22.33203125" style="13" customWidth="1"/>
+    <col min="13" max="16382" width="11.5546875" style="13"/>
+    <col min="16383" max="16384" width="11.5546875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="15" t="s">
         <v>116</v>
       </c>
@@ -1868,43 +1857,39 @@
         <v>106</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="G1" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>109</v>
       </c>
+      <c r="I1" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="J1" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="L1" s="13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:11">
       <c r="A6" s="15"/>
       <c r="B6" s="19"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
       <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/auto_repair/public/www/assets/xlsx/si-6.xlsx
+++ b/auto_repair/public/www/assets/xlsx/si-6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abees\Documents\sic\auto-repair-erp\web\src\assets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656B2AB4-843D-46E1-91CF-15469E79002C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B213D5-0F26-4BDD-B498-EA6B9D38ED79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiscal Years" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="Suppliers" sheetId="13" r:id="rId13"/>
     <sheet name="Invoices" sheetId="20" r:id="rId14"/>
     <sheet name="Presets" sheetId="15" r:id="rId15"/>
-    <sheet name="Sheet1" sheetId="19" r:id="rId16"/>
+    <sheet name="Vehicles" sheetId="19" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Journal Entries'!$A$1:$E$5</definedName>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="136">
   <si>
     <t>year</t>
   </si>
@@ -432,6 +432,39 @@
   </si>
   <si>
     <t>Is Recycable</t>
+  </si>
+  <si>
+    <t>plate_number</t>
+  </si>
+  <si>
+    <t>plate_code</t>
+  </si>
+  <si>
+    <t>chassis</t>
+  </si>
+  <si>
+    <t>make</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>insurance_company</t>
+  </si>
+  <si>
+    <t>insurance_issue_date</t>
+  </si>
+  <si>
+    <t>insurance_expiry_date</t>
+  </si>
+  <si>
+    <t>registration_issue_date</t>
+  </si>
+  <si>
+    <t>registration_expiry_date</t>
   </si>
 </sst>
 </file>
@@ -1431,9 +1464,58 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3F57ED5-7504-4141-956C-6DCB4570F3E3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" customWidth="1"/>
+    <col min="10" max="10" width="20.44140625" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" customWidth="1"/>
+    <col min="12" max="12" width="22.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
